--- a/INSTANCES/OAMRP-Data/20-aircraft/667FL_20A.xlsx
+++ b/INSTANCES/OAMRP-Data/20-aircraft/667FL_20A.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="75">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -173,42 +173,6 @@
   </si>
   <si>
     <t xml:space="preserve">T_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BZI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KYA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAJ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TEQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XHQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YEI</t>
   </si>
   <si>
     <t xml:space="preserve">TAIL_NUMBER</t>
@@ -567,7 +531,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H668"/>
-  <sheetFormatPr defaultColWidth="10.44140625" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.4453125" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -17975,16 +17939,16 @@
       <c r="F1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -18007,16 +17971,16 @@
       <c r="F2" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>372</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <v>78</v>
       </c>
-      <c r="J2" s="0" t="n">
+      <c r="J2" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -18036,7 +18000,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="10.5859375" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -18073,25 +18037,25 @@
         <v>10</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18099,908 +18063,102 @@
         <v>12</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H32" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="H36" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19025,24 +18183,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -19053,7 +18211,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -19064,7 +18222,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -19075,7 +18233,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -19084,7 +18242,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -19093,7 +18251,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -19102,7 +18260,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -19111,7 +18269,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -19120,62 +18278,62 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
